--- a/data/trans_orig/P1419-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2007</t>
+          <t>Población con diagnóstico de varices en las piernas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>15579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>52043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452021</t>
+          <t>450968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466833</t>
+          <t>465959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272159</t>
+          <t>271020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290553</t>
+          <t>291101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728362</t>
+          <t>728414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753830</t>
+          <t>753361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>34257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23041</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350522</t>
+          <t>350503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362942</t>
+          <t>362667</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336303</t>
+          <t>337608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355608</t>
+          <t>355921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692652</t>
+          <t>692611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715758</t>
+          <t>715400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511761</t>
+          <t>511580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529758</t>
+          <t>529462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138162</t>
+          <t>137089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>154934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655768</t>
+          <t>654631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681022</t>
+          <t>680689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26679</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50123</t>
+          <t>50673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>94254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94493</t>
+          <t>94749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136345</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1188211</t>
+          <t>1187661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1211655</t>
+          <t>1212172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>619393</t>
+          <t>620031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>653062</t>
+          <t>652841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1816275</t>
+          <t>1815815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1858127</t>
+          <t>1857871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>27878</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42955</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72821</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>57260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93883</t>
+          <t>93632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>320961</t>
+          <t>322677</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>339735</t>
+          <t>340540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>495931</t>
+          <t>494939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525797</t>
+          <t>525211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>825424</t>
+          <t>825675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>860161</t>
+          <t>862047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141072</t>
+          <t>142504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>185496</t>
+          <t>192621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141150</t>
+          <t>143660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189359</t>
+          <t>190029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291187</t>
+          <t>291575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1063264</t>
+          <t>1056139</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1107688</t>
+          <t>1106256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1357601</t>
+          <t>1356931</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1405810</t>
+          <t>1403300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118887</t>
+          <t>122441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>329448</t>
+          <t>334234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>402303</t>
+          <t>402735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>423482</t>
+          <t>422146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>503938</t>
+          <t>506949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3151303</t>
+          <t>3147749</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3190601</t>
+          <t>3188975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2975821</t>
+          <t>2975389</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3048676</t>
+          <t>3043890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6144376</t>
+          <t>6141365</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6224832</t>
+          <t>6226168</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2012</t>
+          <t>Población con diagnóstico de varices en las piernas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>17755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431540</t>
+          <t>431660</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296763</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309645</t>
+          <t>309573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>733746</t>
+          <t>733123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745798</t>
+          <t>746166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>33160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408587</t>
+          <t>409517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417741</t>
+          <t>417750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309458</t>
+          <t>309154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327795</t>
+          <t>327055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>721202</t>
+          <t>723648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742909</t>
+          <t>743423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16019</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31607</t>
+          <t>31126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>19682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41048</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613396</t>
+          <t>613159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626222</t>
+          <t>625387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228522</t>
+          <t>229003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247291</t>
+          <t>247404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848496</t>
+          <t>846815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>869653</t>
+          <t>869862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64455</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>55398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90384</t>
+          <t>91328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1122844</t>
+          <t>1122409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144814</t>
+          <t>1144194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700267</t>
+          <t>700927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729197</t>
+          <t>729100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1833347</t>
+          <t>1832403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1869048</t>
+          <t>1868333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62492</t>
+          <t>62396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96654</t>
+          <t>97844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65339</t>
+          <t>65365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102602</t>
+          <t>100737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500058</t>
+          <t>500254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509563</t>
+          <t>509559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>663592</t>
+          <t>662402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697754</t>
+          <t>697850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1168241</t>
+          <t>1170106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1205504</t>
+          <t>1205478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106704</t>
+          <t>105095</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>149200</t>
+          <t>147714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104962</t>
+          <t>103816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150729</t>
+          <t>148124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>960151</t>
+          <t>961637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1002647</t>
+          <t>1004256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1225504</t>
+          <t>1228109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1271271</t>
+          <t>1272417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58014</t>
+          <t>56135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>269127</t>
+          <t>264533</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>334130</t>
+          <t>334297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306147</t>
+          <t>306667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>378731</t>
+          <t>382766</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3363896</t>
+          <t>3365775</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3392225</t>
+          <t>3393714</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3212785</t>
+          <t>3212618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3277788</t>
+          <t>3282382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6590094</t>
+          <t>6586059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6662678</t>
+          <t>6662158</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2016</t>
+          <t>Población con diagnóstico de varices en las piernas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>37031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411026</t>
+          <t>410009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424736</t>
+          <t>424425</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>322998</t>
+          <t>323001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340445</t>
+          <t>340566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739622</t>
+          <t>739116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762026</t>
+          <t>761631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366925</t>
+          <t>367582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376272</t>
+          <t>376274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353067</t>
+          <t>354284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368087</t>
+          <t>368080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727131</t>
+          <t>726814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742603</t>
+          <t>742532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>41693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501543</t>
+          <t>501187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515568</t>
+          <t>515790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138860</t>
+          <t>137974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155823</t>
+          <t>156197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644700</t>
+          <t>646343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668727</t>
+          <t>668796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>28034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55429</t>
+          <t>54421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41053</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>71033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125267</t>
+          <t>1125378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1141535</t>
+          <t>1141168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>770447</t>
+          <t>771455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>797429</t>
+          <t>797842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1902563</t>
+          <t>1904481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1934461</t>
+          <t>1934639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19207</t>
+          <t>19468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45608</t>
+          <t>44138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75984</t>
+          <t>74483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57084</t>
+          <t>57008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>90972</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601499</t>
+          <t>601238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614944</t>
+          <t>614754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662260</t>
+          <t>663761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>692636</t>
+          <t>694106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1268464</t>
+          <t>1267978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1301866</t>
+          <t>1301942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60079</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96294</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59219</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97154</t>
+          <t>97742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281972</t>
+          <t>282512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985731</t>
+          <t>985349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1021946</t>
+          <t>1023466</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1272016</t>
+          <t>1271428</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1309951</t>
+          <t>1309153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39306</t>
+          <t>39502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68083</t>
+          <t>67595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188368</t>
+          <t>188189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249429</t>
+          <t>249091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237704</t>
+          <t>234530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307376</t>
+          <t>306153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3317639</t>
+          <t>3318127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3346416</t>
+          <t>3346220</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3282167</t>
+          <t>3282505</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3343228</t>
+          <t>3343407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6609942</t>
+          <t>6611165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6679614</t>
+          <t>6682788</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2023</t>
+          <t>Población con diagnóstico de varices en las piernas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37273</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61234</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>480115</t>
+          <t>479967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495644</t>
+          <t>495447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406607</t>
+          <t>406019</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423146</t>
+          <t>423605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>891445</t>
+          <t>892253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>915406</t>
+          <t>915369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39080</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35146</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>56843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430307</t>
+          <t>429966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443541</t>
+          <t>443359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>342831</t>
+          <t>343165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358554</t>
+          <t>358724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777649</t>
+          <t>777281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798978</t>
+          <t>798619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44938</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>23933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>39962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86240</t>
+          <t>86913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622607</t>
+          <t>620166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659814</t>
+          <t>658405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>126949</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143171</t>
+          <t>142978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>748216</t>
+          <t>747543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>810903</t>
+          <t>807279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40357</t>
+          <t>39669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>66070</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104469</t>
+          <t>104988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88520</t>
+          <t>93355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154702</t>
+          <t>155849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>968447</t>
+          <t>968749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>994462</t>
+          <t>995150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>872901</t>
+          <t>872382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>936258</t>
+          <t>935719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857487</t>
+          <t>1856340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923669</t>
+          <t>1918834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85653</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135617</t>
+          <t>135357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104018</t>
+          <t>102551</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147638</t>
+          <t>146192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454537</t>
+          <t>453989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466647</t>
+          <t>466444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703379</t>
+          <t>703639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753343</t>
+          <t>753581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165407</t>
+          <t>1166853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209027</t>
+          <t>1210494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84663</t>
+          <t>86856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59173</t>
+          <t>59113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>86088</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236732</t>
+          <t>237218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>676029</t>
+          <t>673836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>701325</t>
+          <t>701781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915035</t>
+          <t>915112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942027</t>
+          <t>942087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90998</t>
+          <t>94178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>142698</t>
+          <t>143855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>296574</t>
+          <t>296506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>395921</t>
+          <t>394680</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418089</t>
+          <t>409223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525781</t>
+          <t>522293</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3231647</t>
+          <t>3230490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3283347</t>
+          <t>3280167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3177426</t>
+          <t>3178667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3276773</t>
+          <t>3276841</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6421911</t>
+          <t>6425399</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6529603</t>
+          <t>6538469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1419-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15579</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27096</t>
+          <t>27156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450968</t>
+          <t>451568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465959</t>
+          <t>466876</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271020</t>
+          <t>270871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291101</t>
+          <t>291410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>728414</t>
+          <t>727729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>753361</t>
+          <t>753301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24246</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16464</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35169</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>33091</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>46102</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24246</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15944</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34257</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>33091</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>23399</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>46188</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350503</t>
+          <t>350420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362667</t>
+          <t>362884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>347619</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>336696</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>355401</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>705708</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>692697</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>715225</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>95,52%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>347619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>337608</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>355921</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>705708</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>692611</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>715400</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>13070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30809</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>13024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>30098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29482</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55540</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511580</t>
+          <t>511431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529462</t>
+          <t>529319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137089</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154934</t>
+          <t>154758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>654631</t>
+          <t>655961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680689</t>
+          <t>680925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94254</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>94051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136805</t>
+          <t>134946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1187661</t>
+          <t>1189013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1212172</t>
+          <t>1212768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>620031</t>
+          <t>620100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>652841</t>
+          <t>653471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1815815</t>
+          <t>1817674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1857871</t>
+          <t>1858569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27878</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73813</t>
+          <t>73674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57260</t>
+          <t>58893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93632</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322677</t>
+          <t>321415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340540</t>
+          <t>339910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>494939</t>
+          <t>495078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525211</t>
+          <t>524694</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>825675</t>
+          <t>825026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>862047</t>
+          <t>860414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142504</t>
+          <t>140885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>192621</t>
+          <t>187049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143660</t>
+          <t>142742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190029</t>
+          <t>190478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291575</t>
+          <t>291941</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056139</t>
+          <t>1061711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1106256</t>
+          <t>1107875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1356931</t>
+          <t>1356482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1403300</t>
+          <t>1404218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>80126</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122441</t>
+          <t>120790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334234</t>
+          <t>332065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>402735</t>
+          <t>403068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>422146</t>
+          <t>419946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>506949</t>
+          <t>504010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147749</t>
+          <t>3149400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3188975</t>
+          <t>3190064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2975389</t>
+          <t>2975056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3043890</t>
+          <t>3046059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6141365</t>
+          <t>6144304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6226168</t>
+          <t>6228368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431660</t>
+          <t>432898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296699</t>
+          <t>296550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>309413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>733123</t>
+          <t>732736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746166</t>
+          <t>745757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28857</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409517</t>
+          <t>408840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>417750</t>
+          <t>417749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309154</t>
+          <t>310291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327055</t>
+          <t>327510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723648</t>
+          <t>723174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743423</t>
+          <t>743050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31126</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>18430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613159</t>
+          <t>612282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625387</t>
+          <t>625328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>229003</t>
+          <t>228322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>247404</t>
+          <t>246809</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>846815</t>
+          <t>847170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>869862</t>
+          <t>871114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14815</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>35527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>35181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>64829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55398</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91328</t>
+          <t>90488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1122409</t>
+          <t>1123482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1144194</t>
+          <t>1144496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>700927</t>
+          <t>699893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729100</t>
+          <t>729541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832403</t>
+          <t>1833243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1868333</t>
+          <t>1868284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62396</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97844</t>
+          <t>96195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65365</t>
+          <t>64786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100737</t>
+          <t>102391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500254</t>
+          <t>499356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509559</t>
+          <t>509549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662402</t>
+          <t>664051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697850</t>
+          <t>697474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1170106</t>
+          <t>1168452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1205478</t>
+          <t>1206057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>105095</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>147714</t>
+          <t>148746</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103816</t>
+          <t>103847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148124</t>
+          <t>148705</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>961637</t>
+          <t>960605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1004256</t>
+          <t>1004647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1228109</t>
+          <t>1227528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1272417</t>
+          <t>1272386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56135</t>
+          <t>55647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>264533</t>
+          <t>266688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>334297</t>
+          <t>333483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>306667</t>
+          <t>303408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>382766</t>
+          <t>377130</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3365775</t>
+          <t>3366263</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3393714</t>
+          <t>3393508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3212618</t>
+          <t>3213432</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3282382</t>
+          <t>3280227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6586059</t>
+          <t>6591695</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6662158</t>
+          <t>6665417</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24054</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37031</t>
+          <t>35847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410009</t>
+          <t>409521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424425</t>
+          <t>424078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323001</t>
+          <t>324468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340566</t>
+          <t>340164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739116</t>
+          <t>740300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>761631</t>
+          <t>761718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9645</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>367582</t>
+          <t>367536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376274</t>
+          <t>376266</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354284</t>
+          <t>354099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368080</t>
+          <t>368169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726814</t>
+          <t>726620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742532</t>
+          <t>742591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28149</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41693</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501187</t>
+          <t>501555</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515790</t>
+          <t>515791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137974</t>
+          <t>138691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156197</t>
+          <t>155671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646343</t>
+          <t>645649</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668796</t>
+          <t>668573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54421</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40875</t>
+          <t>39851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71033</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125378</t>
+          <t>1125219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1141168</t>
+          <t>1141733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>771455</t>
+          <t>771999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>797842</t>
+          <t>797029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1904481</t>
+          <t>1904303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1934639</t>
+          <t>1935663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19468</t>
+          <t>20436</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>45600</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74483</t>
+          <t>77468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57008</t>
+          <t>54268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90972</t>
+          <t>90805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601238</t>
+          <t>600270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614754</t>
+          <t>614472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>663761</t>
+          <t>660776</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694106</t>
+          <t>692644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1267978</t>
+          <t>1268145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1301942</t>
+          <t>1304682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58559</t>
+          <t>58522</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96676</t>
+          <t>95578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97742</t>
+          <t>96440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282512</t>
+          <t>282756</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>985349</t>
+          <t>986447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1023466</t>
+          <t>1023503</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1271428</t>
+          <t>1272730</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1309153</t>
+          <t>1309329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39502</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>70264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>188189</t>
+          <t>187814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249091</t>
+          <t>246126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>234530</t>
+          <t>234666</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>306153</t>
+          <t>306896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3318127</t>
+          <t>3315458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3346220</t>
+          <t>3346580</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3282505</t>
+          <t>3285470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3343407</t>
+          <t>3343782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6611165</t>
+          <t>6610422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6682788</t>
+          <t>6682652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>19043</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31822</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47783</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>43125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60426</t>
+          <t>68837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>489251</t>
+          <t>531575</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>479967</t>
+          <t>521745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>495447</t>
+          <t>538742</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>415645</t>
+          <t>452866</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406019</t>
+          <t>442256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423605</t>
+          <t>461913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>904896</t>
+          <t>984441</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>892253</t>
+          <t>970192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>915369</t>
+          <t>995904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>23877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30594</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45008</t>
+          <t>50614</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56843</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>437799</t>
+          <t>467862</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429966</t>
+          <t>459335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443359</t>
+          <t>473895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>351317</t>
+          <t>387227</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343165</t>
+          <t>376936</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358724</t>
+          <t>395238</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>789116</t>
+          <t>855090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>777281</t>
+          <t>842722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798619</t>
+          <t>866491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>27664</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47379</t>
+          <t>40285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23933</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>44406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>63064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>50925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>77909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>642050</t>
+          <t>443079</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620166</t>
+          <t>430458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658405</t>
+          <t>451714</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135629</t>
+          <t>152097</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126949</t>
+          <t>143091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142978</t>
+          <t>159617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>777679</t>
+          <t>595177</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>747543</t>
+          <t>580332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>807279</t>
+          <t>607316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52296</t>
+          <t>58453</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>46284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66070</t>
+          <t>74726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>88754</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>75767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104988</t>
+          <t>103595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>147207</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93355</t>
+          <t>129397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155849</t>
+          <t>168437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>982523</t>
+          <t>1073390</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>968749</t>
+          <t>1057117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>995150</t>
+          <t>1085559</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>898726</t>
+          <t>771754</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>872382</t>
+          <t>756913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>935719</t>
+          <t>784741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1881249</t>
+          <t>1845144</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1856340</t>
+          <t>1823914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1918834</t>
+          <t>1862954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977370</t>
+          <t>860508</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977370</t>
+          <t>860508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977370</t>
+          <t>860508</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012189</t>
+          <t>1992351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012189</t>
+          <t>1992351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012189</t>
+          <t>1992351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>114602</t>
+          <t>126034</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>109727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135357</t>
+          <t>142970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>127156</t>
+          <t>139545</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102551</t>
+          <t>121883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146192</t>
+          <t>160149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>461495</t>
+          <t>553465</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453989</t>
+          <t>544820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466444</t>
+          <t>559273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>724394</t>
+          <t>704093</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>703639</t>
+          <t>687157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753581</t>
+          <t>720400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1185889</t>
+          <t>1257558</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1166853</t>
+          <t>1236954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1210494</t>
+          <t>1275220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>570</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70996</t>
+          <t>76254</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58911</t>
+          <t>63680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86856</t>
+          <t>92033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71530</t>
+          <t>76825</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>64670</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86088</t>
+          <t>93368</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239973</t>
+          <t>236658</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237218</t>
+          <t>234273</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>689696</t>
+          <t>767342</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>673836</t>
+          <t>751563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>701781</t>
+          <t>779916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>929670</t>
+          <t>1003999</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>915112</t>
+          <t>987456</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942087</t>
+          <t>1016154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>121254</t>
+          <t>134591</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94178</t>
+          <t>113813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143855</t>
+          <t>156604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>357940</t>
+          <t>397252</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>296506</t>
+          <t>368414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>394680</t>
+          <t>427727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>479194</t>
+          <t>531844</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409223</t>
+          <t>494289</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>522293</t>
+          <t>572590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3253091</t>
+          <t>3306029</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3230490</t>
+          <t>3284016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3280167</t>
+          <t>3326807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3215407</t>
+          <t>3235379</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3178667</t>
+          <t>3204904</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3276841</t>
+          <t>3264217</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6468498</t>
+          <t>6541407</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6425399</t>
+          <t>6500661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6538469</t>
+          <t>6578962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374345</t>
+          <t>3440620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374345</t>
+          <t>3440620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374345</t>
+          <t>3440620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573347</t>
+          <t>3632631</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573347</t>
+          <t>3632631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573347</t>
+          <t>3632631</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947692</t>
+          <t>7073251</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947692</t>
+          <t>7073251</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947692</t>
+          <t>7073251</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
